--- a/morpg/morpg/Assets/TableData/Table_Item.xlsx
+++ b/morpg/morpg/Assets/TableData/Table_Item.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fileVersion appName="HCell" lastEdited="12.0" lowestEdited="12.0" rupBuild="0.4426"/>
+  <x:fileVersion appName="HCell" lastEdited="12.0" lowestEdited="12.0" rupBuild="0.4547"/>
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" Requires="x15">
@@ -19,7 +19,79 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="36">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="38">
+  <x:si>
+    <x:t>Equipment009</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Etc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Etc001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gloves</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Armor</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Etc004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Head</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Etc005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Consume</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Etc002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Index</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Comment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Array</x:t>
+  </x:si>
+  <x:si>
+    <x:t>None</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ring</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Boots</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Weapon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Etc003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Earring</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Consume002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Equipment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Category</x:t>
+  </x:si>
   <x:si>
     <x:t>Consume001</x:t>
   </x:si>
@@ -30,103 +102,37 @@
     <x:t>Necklace</x:t>
   </x:si>
   <x:si>
-    <x:t>Consume002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Equipment</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Category</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Etc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Head</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Etc005</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Consume</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Etc001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Gloves</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Armor</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Etc004</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Array</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Etc003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ring</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Earring</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Index</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Etc002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Boots</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Comment</x:t>
-  </x:si>
-  <x:si>
-    <x:t>None</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Weapon</x:t>
+    <x:t>Shield</x:t>
   </x:si>
   <x:si>
     <x:t>EquipmentEnum</x:t>
   </x:si>
   <x:si>
+    <x:t>Equipment004</x:t>
+  </x:si>
+  <x:si>
     <x:t>Equipment001</x:t>
   </x:si>
   <x:si>
-    <x:t>Equipment004</x:t>
-  </x:si>
-  <x:si>
     <x:t>Equipment006</x:t>
   </x:si>
   <x:si>
     <x:t>CategoryEnum</x:t>
   </x:si>
   <x:si>
+    <x:t>Equipment008</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Equipment007</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Equipment005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Equipment003</x:t>
+  </x:si>
+  <x:si>
     <x:t>Equipment002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Equipment008</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Equipment007</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Equipment005</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Equipment003</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -897,7 +903,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:G44"/>
+  <x:dimension ref="A1:G45"/>
   <x:sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="16.39999999999999857891"/>
   <x:cols>
     <x:col min="1" max="1" width="8.796875" bestFit="1" customWidth="1"/>
@@ -910,16 +916,16 @@
   <x:sheetData>
     <x:row r="1" spans="1:7">
       <x:c r="A1" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E1" s="1"/>
       <x:c r="F1" s="7"/>
@@ -927,16 +933,16 @@
     </x:row>
     <x:row r="2" spans="1:7">
       <x:c r="A2" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E2" s="1"/>
       <x:c r="F2" s="7"/>
@@ -944,7 +950,7 @@
     </x:row>
     <x:row r="3" spans="1:7">
       <x:c r="A3" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B3" s="1"/>
       <x:c r="C3" s="1"/>
@@ -955,7 +961,7 @@
     </x:row>
     <x:row r="4" spans="1:7">
       <x:c r="A4" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B4" s="1"/>
       <x:c r="C4" s="1"/>
@@ -969,13 +975,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B5" s="2" t="s">
-        <x:v>0</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C5" s="2" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E5" s="1"/>
       <x:c r="F5" s="7"/>
@@ -986,13 +992,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B6" s="2" t="s">
-        <x:v>3</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C6" s="2" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E6" s="9"/>
       <x:c r="F6" s="10"/>
@@ -1003,287 +1009,300 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B7" s="2" t="s">
-        <x:v>27</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C7" s="2" t="s">
-        <x:v>4</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E7" s="1"/>
       <x:c r="F7" s="8"/>
     </x:row>
-    <x:row r="8" spans="1:6">
-      <x:c r="A8" s="9">
+    <x:row r="8" spans="1:6" customFormat="1">
+      <x:c r="A8" s="1">
         <x:v>4</x:v>
       </x:c>
       <x:c r="B8" s="2" t="s">
-        <x:v>31</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C8" s="2" t="s">
-        <x:v>4</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E8" s="9"/>
+      <x:c r="F8" s="8"/>
+    </x:row>
+    <x:row r="9" spans="1:6">
+      <x:c r="A9" s="9">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B9" s="2" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C9" s="2" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D9" s="1" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="E8" s="1"/>
-      <x:c r="F8" s="7"/>
-    </x:row>
-    <x:row r="9" spans="1:6">
-      <x:c r="A9" s="1">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B9" s="2" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C9" s="2" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D9" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
       <x:c r="E9" s="1"/>
-      <x:c r="F9" s="8"/>
+      <x:c r="F9" s="7"/>
     </x:row>
     <x:row r="10" spans="1:6">
-      <x:c r="A10" s="9">
+      <x:c r="A10" s="1">
         <x:v>6</x:v>
       </x:c>
       <x:c r="B10" s="2" t="s">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C10" s="2" t="s">
-        <x:v>4</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E10" s="1"/>
-      <x:c r="F10" s="7"/>
+      <x:c r="F10" s="8"/>
     </x:row>
     <x:row r="11" spans="1:6">
       <x:c r="A11" s="1">
         <x:v>7</x:v>
       </x:c>
       <x:c r="B11" s="2" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C11" s="2" t="s">
-        <x:v>4</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E11" s="1"/>
-      <x:c r="F11" s="8"/>
+      <x:c r="F11" s="7"/>
     </x:row>
     <x:row r="12" spans="1:6">
       <x:c r="A12" s="9">
         <x:v>8</x:v>
       </x:c>
       <x:c r="B12" s="2" t="s">
-        <x:v>29</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C12" s="2" t="s">
-        <x:v>4</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E12" s="1"/>
-      <x:c r="F12" s="7"/>
+      <x:c r="F12" s="8"/>
     </x:row>
     <x:row r="13" spans="1:6">
       <x:c r="A13" s="1">
         <x:v>9</x:v>
       </x:c>
       <x:c r="B13" s="2" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C13" s="2" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D13" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E13" s="1"/>
+      <x:c r="F13" s="7"/>
+    </x:row>
+    <x:row r="14" spans="1:6">
+      <x:c r="A14" s="1">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B14" s="2" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C13" s="2" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D13" s="2" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="E13" s="1"/>
-      <x:c r="F13" s="8"/>
-    </x:row>
-    <x:row r="14" spans="1:6">
-      <x:c r="A14" s="9">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B14" s="2" t="s">
-        <x:v>32</x:v>
-      </x:c>
       <x:c r="C14" s="2" t="s">
-        <x:v>4</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D14" s="2" t="s">
-        <x:v>2</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E14" s="1"/>
-      <x:c r="F14" s="7"/>
+      <x:c r="F14" s="8"/>
     </x:row>
     <x:row r="15" spans="1:6">
-      <x:c r="A15" s="2">
+      <x:c r="A15" s="9">
         <x:v>11</x:v>
       </x:c>
       <x:c r="B15" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C15" s="2" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D15" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D15" s="2" t="s">
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E15" s="1"/>
-      <x:c r="F15" s="8"/>
+      <x:c r="F15" s="7"/>
     </x:row>
     <x:row r="16" spans="1:6">
       <x:c r="A16" s="1">
         <x:v>12</x:v>
       </x:c>
       <x:c r="B16" s="2" t="s">
-        <x:v>21</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C16" s="2" t="s">
-        <x:v>6</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E16" s="1"/>
-      <x:c r="F16" s="7"/>
+      <x:c r="F16" s="8"/>
     </x:row>
     <x:row r="17" spans="1:6">
-      <x:c r="A17">
+      <x:c r="A17" s="1">
         <x:v>13</x:v>
       </x:c>
       <x:c r="B17" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C17" s="2" t="s">
-        <x:v>6</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="E17" s="3"/>
-      <x:c r="F17" s="8"/>
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E17" s="1"/>
+      <x:c r="F17" s="7"/>
     </x:row>
     <x:row r="18" spans="1:6">
-      <x:c r="A18" s="1">
+      <x:c r="A18" s="9">
         <x:v>14</x:v>
       </x:c>
       <x:c r="B18" s="2" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C18" s="2" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D18" s="1" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C18" s="2" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D18" s="1" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="E18" s="1"/>
-      <x:c r="F18" s="7"/>
+      <x:c r="E18" s="3"/>
+      <x:c r="F18" s="8"/>
     </x:row>
     <x:row r="19" spans="1:6">
-      <x:c r="A19">
+      <x:c r="A19" s="1">
         <x:v>15</x:v>
       </x:c>
       <x:c r="B19" s="2" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C19" s="2" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D19" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E19" s="1"/>
+      <x:c r="F19" s="7"/>
+    </x:row>
+    <x:row r="20" spans="1:6">
+      <x:c r="A20" s="1">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B20" s="2" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C19" s="2" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D19" s="1" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="E19" s="1"/>
-      <x:c r="F19" s="8"/>
-    </x:row>
-    <x:row r="20" spans="1:6">
-      <x:c r="A20" s="1"/>
-      <x:c r="B20" s="1"/>
-      <x:c r="C20" s="1"/>
-      <x:c r="E20" s="4"/>
-      <x:c r="F20" s="7"/>
-    </x:row>
-    <x:row r="21" spans="2:6">
+      <x:c r="C20" s="2" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D20" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E20" s="1"/>
+      <x:c r="F20" s="8"/>
+    </x:row>
+    <x:row r="21" spans="1:6">
+      <x:c r="A21" s="1"/>
       <x:c r="B21" s="1"/>
       <x:c r="C21" s="1"/>
-      <x:c r="E21" s="2"/>
-      <x:c r="F21" s="8"/>
-    </x:row>
-    <x:row r="22" spans="1:6">
-      <x:c r="A22" s="1"/>
+      <x:c r="E21" s="4"/>
+      <x:c r="F21" s="7"/>
+    </x:row>
+    <x:row r="22" spans="2:6">
       <x:c r="B22" s="1"/>
       <x:c r="C22" s="1"/>
-      <x:c r="F22" s="7"/>
-    </x:row>
-    <x:row r="23" spans="2:6">
+      <x:c r="E22" s="2"/>
+      <x:c r="F22" s="8"/>
+    </x:row>
+    <x:row r="23" spans="1:6">
+      <x:c r="A23" s="1"/>
       <x:c r="B23" s="1"/>
       <x:c r="C23" s="1"/>
-      <x:c r="E23" s="2"/>
-      <x:c r="F23" s="8"/>
-    </x:row>
-    <x:row r="24" spans="1:6">
-      <x:c r="A24" s="1"/>
+      <x:c r="F23" s="7"/>
+    </x:row>
+    <x:row r="24" spans="2:6">
       <x:c r="B24" s="1"/>
       <x:c r="C24" s="1"/>
-      <x:c r="E24" s="5"/>
-      <x:c r="F24" s="7"/>
-    </x:row>
-    <x:row r="25" spans="2:6">
+      <x:c r="E24" s="2"/>
+      <x:c r="F24" s="8"/>
+    </x:row>
+    <x:row r="25" spans="1:6">
+      <x:c r="A25" s="1"/>
       <x:c r="B25" s="1"/>
       <x:c r="C25" s="1"/>
-      <x:c r="E25" s="1"/>
-      <x:c r="F25" s="8"/>
-    </x:row>
-    <x:row r="26" spans="1:6">
-      <x:c r="A26" s="1"/>
+      <x:c r="E25" s="5"/>
+      <x:c r="F25" s="7"/>
+    </x:row>
+    <x:row r="26" spans="2:6">
       <x:c r="B26" s="1"/>
       <x:c r="C26" s="1"/>
-      <x:c r="E26" s="4"/>
-      <x:c r="F26" s="7"/>
-    </x:row>
-    <x:row r="27" spans="2:6">
+      <x:c r="E26" s="1"/>
+      <x:c r="F26" s="8"/>
+    </x:row>
+    <x:row r="27" spans="1:6">
+      <x:c r="A27" s="1"/>
       <x:c r="B27" s="1"/>
       <x:c r="C27" s="1"/>
-      <x:c r="E27" s="2"/>
-      <x:c r="F27" s="8"/>
-    </x:row>
-    <x:row r="28" spans="1:6">
-      <x:c r="A28" s="1"/>
+      <x:c r="E27" s="4"/>
+      <x:c r="F27" s="7"/>
+    </x:row>
+    <x:row r="28" spans="2:6">
       <x:c r="B28" s="1"/>
       <x:c r="C28" s="1"/>
-      <x:c r="F28" s="7"/>
-    </x:row>
-    <x:row r="29" spans="2:6">
+      <x:c r="E28" s="2"/>
+      <x:c r="F28" s="8"/>
+    </x:row>
+    <x:row r="29" spans="1:6">
+      <x:c r="A29" s="1"/>
       <x:c r="B29" s="1"/>
       <x:c r="C29" s="1"/>
-      <x:c r="E29" s="2"/>
-      <x:c r="F29" s="8"/>
-    </x:row>
-    <x:row r="30" spans="1:6">
-      <x:c r="A30" s="1"/>
+      <x:c r="F29" s="7"/>
+    </x:row>
+    <x:row r="30" spans="2:6">
       <x:c r="B30" s="1"/>
       <x:c r="C30" s="1"/>
-      <x:c r="E30" s="5"/>
-      <x:c r="F30" s="7"/>
-    </x:row>
-    <x:row r="31" spans="2:6">
+      <x:c r="E30" s="2"/>
+      <x:c r="F30" s="8"/>
+    </x:row>
+    <x:row r="31" spans="1:6">
+      <x:c r="A31" s="1"/>
       <x:c r="B31" s="1"/>
       <x:c r="C31" s="1"/>
-      <x:c r="E31" s="1"/>
-      <x:c r="F31" s="8"/>
-    </x:row>
-    <x:row r="32" spans="4:4">
-      <x:c r="D32" s="2"/>
+      <x:c r="E31" s="5"/>
+      <x:c r="F31" s="7"/>
+    </x:row>
+    <x:row r="32" spans="2:6">
+      <x:c r="B32" s="1"/>
+      <x:c r="C32" s="1"/>
+      <x:c r="E32" s="1"/>
+      <x:c r="F32" s="8"/>
     </x:row>
     <x:row r="33" spans="4:4">
       <x:c r="D33" s="2"/>
@@ -1320,6 +1339,9 @@
     </x:row>
     <x:row r="44" spans="4:4">
       <x:c r="D44" s="2"/>
+    </x:row>
+    <x:row r="45" spans="4:4">
+      <x:c r="D45" s="2"/>
     </x:row>
   </x:sheetData>
   <x:sortState columnSort="0" caseSensitive="0" ref="D6:E30">
